--- a/template.xlsx
+++ b/template.xlsx
@@ -81,10 +81,10 @@
     <t>SUBTOTAL DESPESAS PARA REEMBOLSO:</t>
   </si>
   <si>
-    <t>DESPESAS CARTÃO ALELO</t>
+    <t>DESPESAS CARTÃO SANTANDER - SOMA</t>
   </si>
   <si>
-    <t>SUBTOTAL DESPESAS PARA CARTÃO ALELO:</t>
+    <t>SUBTOTAL DESPESAS CARTÃO SANTANDER - SOMA:</t>
   </si>
   <si>
     <t>TOTAL DOS GASTOS</t>
